--- a/life.xlsx
+++ b/life.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1902" uniqueCount="1646">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1915" uniqueCount="1658">
   <si>
     <t>Мисъл</t>
   </si>
@@ -7607,18 +7607,62 @@
   </si>
   <si>
     <t>Добра вечеря</t>
+  </si>
+  <si>
+    <t>Аз</t>
+  </si>
+  <si>
+    <t>Комуникативни умения</t>
+  </si>
+  <si>
+    <t>Връзки</t>
+  </si>
+  <si>
+    <t>Клиенти</t>
+  </si>
+  <si>
+    <t>Васко и Иво</t>
+  </si>
+  <si>
+    <t>Жоро и Марко</t>
+  </si>
+  <si>
+    <t>Колеги</t>
+  </si>
+  <si>
+    <t>Агенти</t>
+  </si>
+  <si>
+    <t>Предприемачи</t>
+  </si>
+  <si>
+    <t>Магазина</t>
+  </si>
+  <si>
+    <t>Facebook</t>
+  </si>
+  <si>
+    <t>Реклама</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="33">
+  <fonts count="34">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -8124,93 +8168,93 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
@@ -8225,43 +8269,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="7" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="5" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" quotePrefix="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -14861,12 +14905,12 @@
       <c r="B36" s="4"/>
       <c r="C36" s="99">
         <f ca="1">TODAY()-F32</f>
-        <v>659</v>
+        <v>705</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="98" t="str">
         <f ca="1">DATEDIF(F32,TODAY(),"Y") &amp; " години, " &amp; DATEDIF(F32,TODAY(),"YM") &amp; " месеца, " &amp; DATEDIF(F32,TODAY(),"MD") &amp; " дни"</f>
-        <v>1 години, 9 месеца, 22 дни</v>
+        <v>1 години, 11 месеца, 6 дни</v>
       </c>
       <c r="G36" s="10"/>
       <c r="H36" s="11"/>
@@ -22602,6 +22646,89 @@
       <c r="E67" s="10"/>
       <c r="F67" s="119"/>
     </row>
+    <row r="73" spans="1:8">
+      <c r="B73" s="16" t="s">
+        <v>1646</v>
+      </c>
+      <c r="C73" s="16" t="s">
+        <v>1647</v>
+      </c>
+      <c r="F73" s="16" t="s">
+        <v>1648</v>
+      </c>
+      <c r="H73" s="16" t="s">
+        <v>1649</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="D74">
+        <v>6</v>
+      </c>
+      <c r="E74">
+        <v>2</v>
+      </c>
+      <c r="F74" t="s">
+        <v>1615</v>
+      </c>
+      <c r="H74">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="D75">
+        <v>6</v>
+      </c>
+      <c r="E75">
+        <v>2</v>
+      </c>
+      <c r="F75" t="s">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="D76">
+        <v>6</v>
+      </c>
+      <c r="F76" t="s">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="F77" t="s">
+        <v>1652</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="F78" t="s">
+        <v>1653</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="F79" t="s">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="D80">
+        <v>4</v>
+      </c>
+      <c r="E80">
+        <v>1</v>
+      </c>
+      <c r="F80" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="81" spans="6:6">
+      <c r="F81" t="s">
+        <v>1656</v>
+      </c>
+    </row>
+    <row r="82" spans="6:6">
+      <c r="F82" t="s">
+        <v>1657</v>
+      </c>
+    </row>
     <row r="110" spans="1:2">
       <c r="A110" s="16" t="s">
         <v>1217</v>

--- a/life.xlsx
+++ b/life.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" firstSheet="1" activeTab="8"/>
+    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016" firstSheet="1" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1915" uniqueCount="1658">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1916" uniqueCount="1659">
   <si>
     <t>Мисъл</t>
   </si>
@@ -7643,6 +7643,9 @@
   </si>
   <si>
     <t>Реклама</t>
+  </si>
+  <si>
+    <t>Живяла</t>
   </si>
 </sst>
 </file>
@@ -14759,7 +14762,7 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A2:J48"/>
+  <dimension ref="A2:M48"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="3" max="3" width="14.77734375" bestFit="1" customWidth="1"/>
@@ -14812,7 +14815,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:13">
       <c r="B18" s="96" t="s">
         <v>1474</v>
       </c>
@@ -14826,7 +14829,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:13">
       <c r="C21" s="96" t="s">
         <v>1472</v>
       </c>
@@ -14834,7 +14837,7 @@
         <v>1473</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:13">
       <c r="D24" s="24" t="s">
         <v>1468</v>
       </c>
@@ -14842,17 +14845,17 @@
         <v>1471</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:13">
       <c r="D27" s="24" t="s">
         <v>1461</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:13">
       <c r="A29" s="16" t="s">
         <v>1477</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:13">
       <c r="B31" s="48" t="s">
         <v>1479</v>
       </c>
@@ -14867,9 +14870,14 @@
         <v>1478</v>
       </c>
       <c r="I31" s="5"/>
-      <c r="J31" s="6"/>
-    </row>
-    <row r="32" spans="1:10">
+      <c r="J31" s="5"/>
+      <c r="K31" s="43" t="s">
+        <v>1658</v>
+      </c>
+      <c r="L31" s="5"/>
+      <c r="M31" s="6"/>
+    </row>
+    <row r="32" spans="1:13">
       <c r="B32" s="4"/>
       <c r="C32" s="97">
         <v>16507</v>
@@ -14884,7 +14892,13 @@
       <c r="I32" s="97">
         <v>45556</v>
       </c>
-      <c r="J32" s="11"/>
+      <c r="J32" s="10"/>
+      <c r="K32" s="10" t="str">
+        <f>DATEDIF(C32,F32,"Y") &amp; " години, " &amp; DATEDIF(C32,F32,"YM") &amp; " месеца, " &amp; DATEDIF(C32,F32,"MD") &amp; " дни"</f>
+        <v>79 години, 6 месеца, 8 дни</v>
+      </c>
+      <c r="L32" s="10"/>
+      <c r="M32" s="11"/>
     </row>
     <row r="33" spans="2:8">
       <c r="F33" s="53"/>
@@ -14905,12 +14919,12 @@
       <c r="B36" s="4"/>
       <c r="C36" s="99">
         <f ca="1">TODAY()-F32</f>
-        <v>705</v>
+        <v>725</v>
       </c>
       <c r="E36" s="4"/>
       <c r="F36" s="98" t="str">
         <f ca="1">DATEDIF(F32,TODAY(),"Y") &amp; " години, " &amp; DATEDIF(F32,TODAY(),"YM") &amp; " месеца, " &amp; DATEDIF(F32,TODAY(),"MD") &amp; " дни"</f>
-        <v>1 години, 11 месеца, 6 дни</v>
+        <v>1 години, 11 месеца, 25 дни</v>
       </c>
       <c r="G36" s="10"/>
       <c r="H36" s="11"/>
